--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8941-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8941-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8804D50-7ED5-4EB9-8D42-70A7D2C8EB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A50292F0-BEA3-4BE1-A5BC-37229EA1F2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{396EF03A-C0CD-43B0-A305-B32F7CC94BB1}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C090893F-FEBD-4B49-9812-31126F8BE01C}"/>
   </bookViews>
   <sheets>
     <sheet name="8941-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1616,30 +1616,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5300694E-C349-4DFF-89E8-01780F671E2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE15379-5C85-403B-9EFE-64B96F3B75E6}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="8.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="7" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -1673,7 +1673,7 @@
       <c r="W1" s="35"/>
       <c r="X1" s="27"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
@@ -1709,7 +1709,7 @@
       <c r="W2" s="37"/>
       <c r="X2" s="38"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
         <v>2</v>
       </c>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="X3" s="41"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="30"/>
       <c r="B4" s="31"/>
       <c r="C4" s="7"/>
@@ -1829,7 +1829,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="42">
         <v>2025</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="44">
         <v>2024</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>8.68</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="42">
         <v>2023</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>9.8800000000000008</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="46" t="s">
         <v>29</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="47"/>
       <c r="B13" s="47"/>
       <c r="C13" s="21" t="s">
@@ -2443,7 +2443,7 @@
       <c r="W13" s="53"/>
       <c r="X13" s="49"/>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="44">
         <v>2022</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="42">
         <v>2021</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="44">
         <v>2020</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="54">
         <v>2019</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="56"/>
       <c r="B19" s="57"/>
       <c r="C19" s="22" t="s">
@@ -2833,7 +2833,7 @@
       <c r="W19" s="53"/>
       <c r="X19" s="49"/>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="58">
         <v>2018</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="60"/>
       <c r="B21" s="61"/>
       <c r="C21" s="24" t="s">
@@ -2933,7 +2933,7 @@
       <c r="W21" s="67"/>
       <c r="X21" s="63"/>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="54">
         <v>2017</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="56"/>
       <c r="B23" s="57"/>
       <c r="C23" s="22" t="s">
@@ -3033,7 +3033,7 @@
       <c r="W23" s="53"/>
       <c r="X23" s="49"/>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="44">
         <v>2016</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="42">
         <v>2015</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="44">
         <v>2014</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="42">
         <v>2013</v>
       </c>
@@ -3321,7 +3321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="44">
         <v>2012</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="42">
         <v>2011</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="44">
         <v>2010</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="42">
         <v>2009</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="44">
         <v>2008</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="42">
         <v>2007</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="44">
         <v>2006</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="54">
         <v>2005</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="56"/>
       <c r="B36" s="57"/>
       <c r="C36" s="22" t="s">
@@ -3925,7 +3925,7 @@
       <c r="W36" s="53"/>
       <c r="X36" s="49"/>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="44">
         <v>2004</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="54">
         <v>2003</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="56"/>
       <c r="B39" s="57"/>
       <c r="C39" s="22" t="s">
@@ -4097,7 +4097,7 @@
       <c r="W39" s="53"/>
       <c r="X39" s="49"/>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="58">
         <v>2002</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>7.27</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="60"/>
       <c r="B41" s="61"/>
       <c r="C41" s="24" t="s">
@@ -4197,7 +4197,7 @@
       <c r="W41" s="67"/>
       <c r="X41" s="63"/>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="54">
         <v>2001</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="56"/>
       <c r="B43" s="57"/>
       <c r="C43" s="22" t="s">
@@ -4297,7 +4297,7 @@
       <c r="W43" s="53"/>
       <c r="X43" s="49"/>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="58">
         <v>2000</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="60"/>
       <c r="B45" s="61"/>
       <c r="C45" s="24" t="s">
@@ -4397,7 +4397,7 @@
       <c r="W45" s="67"/>
       <c r="X45" s="63"/>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="42">
         <v>1999</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="44" t="s">
         <v>62</v>
       </c>
